--- a/input_data/input_data_bidcurve.xlsx
+++ b/input_data/input_data_bidcurve.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ADEE6C-3CBC-463C-B872-369776626BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0D92AC-07D2-45A6-8B71-FAC34DF7C259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="8" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="321">
   <si>
     <t>node</t>
   </si>
@@ -1021,6 +1021,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -2208,10 +2211,10 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F824915F-D486-4BD0-AA83-1390B536FEEB}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>315</v>
       </c>
@@ -2229,6 +2232,9 @@
       </c>
       <c r="F1" t="s">
         <v>319</v>
+      </c>
+      <c r="G1" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
